--- a/Result/profitability/2101.xlsx
+++ b/Result/profitability/2101.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.4</v>
       </c>
       <c r="M2" t="n">
-        <v>0.77125</v>
+        <v>0.6575000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>25.3025</v>
+        <v>25.91</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.24</v>
       </c>
       <c r="M3" t="n">
-        <v>0.35125</v>
+        <v>0.6575000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>22.79</v>
+        <v>25.63125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.05</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3875</v>
+        <v>0.6775</v>
       </c>
       <c r="N4" t="n">
-        <v>22.00375</v>
+        <v>24.88</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0.275</v>
+        <v>0.5950000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>19.62</v>
+        <v>22.04625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.02</v>
       </c>
       <c r="M6" t="n">
-        <v>0.31625</v>
+        <v>0.58125</v>
       </c>
       <c r="N6" t="n">
-        <v>17.50875</v>
+        <v>20.445</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.72</v>
       </c>
       <c r="M7" t="n">
-        <v>0.395</v>
+        <v>0.49625</v>
       </c>
       <c r="N7" t="n">
-        <v>17.44875</v>
+        <v>20.25625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.72</v>
       </c>
       <c r="M8" t="n">
-        <v>0.31</v>
+        <v>0.35375</v>
       </c>
       <c r="N8" t="n">
-        <v>17.8975</v>
+        <v>18.1675</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>7626</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4315</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3311</v>
+      </c>
+      <c r="F75" t="n">
+        <v>43.42</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2611</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>34.24%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-888</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1724</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1597</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.9975000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>28.655</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.3499999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1881720430107525</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.160000000000004</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.05235094522540007</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-7.314285714285715</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>19.41</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.8084131611828405</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
